--- a/resultados/tresbarrasdoparana/erros_varredura.xlsx
+++ b/resultados/tresbarrasdoparana/erros_varredura.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2622"/>
+  <dimension ref="A1:F2623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73836,6 +73836,34 @@
         </is>
       </c>
     </row>
+    <row r="2623">
+      <c r="A2623" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B2623" t="inlineStr">
+        <is>
+          <t>https://tresbarras.pr.gov.br/transparencia/atos/decretos/decreto-n-7222-2026</t>
+        </is>
+      </c>
+      <c r="C2623" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D2623" t="n">
+        <v>404</v>
+      </c>
+      <c r="E2623" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2623" t="inlineStr">
+        <is>
+          <t>2026-08-15 09:45:08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/tresbarrasdoparana/erros_varredura.xlsx
+++ b/resultados/tresbarrasdoparana/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2623"/>
+  <dimension ref="A1:F2633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73864,6 +73864,286 @@
         </is>
       </c>
     </row>
+    <row r="2624">
+      <c r="A2624" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B2624" t="inlineStr">
+        <is>
+          <t>https://portal.tresbarras.pr.gov.br/pronimtb/index.asp?acao=1&amp;item=91&amp;visao=0</t>
+        </is>
+      </c>
+      <c r="C2624" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D2624" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2624" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2624" t="inlineStr">
+        <is>
+          <t>2026-08-15 09:59:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="2625">
+      <c r="A2625" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B2625" t="inlineStr">
+        <is>
+          <t>https://portal.tresbarras.pr.gov.br/pronimtb/index.asp?acao=1&amp;item=91&amp;visao=0</t>
+        </is>
+      </c>
+      <c r="C2625" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2625" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2625" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2625" t="inlineStr">
+        <is>
+          <t>2026-08-15 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="2626">
+      <c r="A2626" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B2626" t="inlineStr">
+        <is>
+          <t>https://portal.tresbarras.pr.gov.br/pronimtb/index.asp?acao=1&amp;item=90&amp;visao=0</t>
+        </is>
+      </c>
+      <c r="C2626" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D2626" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2626" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2626" t="inlineStr">
+        <is>
+          <t>2026-08-15 10:00:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="2627">
+      <c r="A2627" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B2627" t="inlineStr">
+        <is>
+          <t>https://portal.tresbarras.pr.gov.br/pronimtb/index.asp?acao=1&amp;item=90&amp;visao=0</t>
+        </is>
+      </c>
+      <c r="C2627" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2627" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2627" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2627" t="inlineStr">
+        <is>
+          <t>2026-08-15 10:00:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="2628">
+      <c r="A2628" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B2628" t="inlineStr">
+        <is>
+          <t>https://portal.tresbarras.pr.gov.br/pronimtb/index.asp?acao=3&amp;item=94&amp;visao=0</t>
+        </is>
+      </c>
+      <c r="C2628" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D2628" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2628" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2628" t="inlineStr">
+        <is>
+          <t>2026-08-15 10:00:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2629">
+      <c r="A2629" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B2629" t="inlineStr">
+        <is>
+          <t>https://portal.tresbarras.pr.gov.br/pronimtb/index.asp?acao=3&amp;item=94&amp;visao=0</t>
+        </is>
+      </c>
+      <c r="C2629" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2629" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2629" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2629" t="inlineStr">
+        <is>
+          <t>2026-08-15 10:00:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2630">
+      <c r="A2630" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B2630" t="inlineStr">
+        <is>
+          <t>https://portal.tresbarras.pr.gov.br/pronimtb/index.asp?acao=3&amp;item=92&amp;visao=0</t>
+        </is>
+      </c>
+      <c r="C2630" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D2630" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2630" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2630" t="inlineStr">
+        <is>
+          <t>2026-08-15 10:00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="2631">
+      <c r="A2631" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B2631" t="inlineStr">
+        <is>
+          <t>https://portal.tresbarras.pr.gov.br/pronimtb/index.asp?acao=3&amp;item=92&amp;visao=0</t>
+        </is>
+      </c>
+      <c r="C2631" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2631" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2631" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2631" t="inlineStr">
+        <is>
+          <t>2026-08-15 10:00:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="2632">
+      <c r="A2632" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B2632" t="inlineStr">
+        <is>
+          <t>http://portal.tresbarras.pr.gov.br/pronimtb/index.asp?acao=4&amp;item=93&amp;visao=0</t>
+        </is>
+      </c>
+      <c r="C2632" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D2632" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2632" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2632" t="inlineStr">
+        <is>
+          <t>2026-08-15 10:00:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="2633">
+      <c r="A2633" t="inlineStr">
+        <is>
+          <t>tresbarrasdoparana</t>
+        </is>
+      </c>
+      <c r="B2633" t="inlineStr">
+        <is>
+          <t>http://portal.tresbarras.pr.gov.br/pronimtb/index.asp?acao=4&amp;item=93&amp;visao=0</t>
+        </is>
+      </c>
+      <c r="C2633" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D2633" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2633" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2633" t="inlineStr">
+        <is>
+          <t>2026-08-15 10:00:53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
